--- a/basedatos_partidas/salida/descompuestos/14.05.01.010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/14.05.01.010.xlsx
@@ -610,10 +610,10 @@
         <v>0.42</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +636,10 @@
         <v>0.32</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="14">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65.98999999999999</v>
+        <v>66.33</v>
       </c>
     </row>
     <row r="16">
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>83.40000000000001</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="27">
@@ -892,7 +892,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>84.23</v>
+        <v>84.58</v>
       </c>
     </row>
   </sheetData>
